--- a/data/trans_orig/P16A_n_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>316400</t>
+          <t>316134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374959</t>
+          <t>373968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>594722</t>
+          <t>588816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>664293</t>
+          <t>662520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>920461</t>
+          <t>927905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1020276</t>
+          <t>1018300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656764</t>
+          <t>657755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>715323</t>
+          <t>715589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650820</t>
+          <t>652593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720391</t>
+          <t>726297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1326559</t>
+          <t>1328535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1426374</t>
+          <t>1418930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136565</t>
+          <t>134719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184963</t>
+          <t>183643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>254317</t>
+          <t>256543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318451</t>
+          <t>314603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>407213</t>
+          <t>405679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484133</t>
+          <t>484675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1508450</t>
+          <t>1509770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1556848</t>
+          <t>1558694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1269222</t>
+          <t>1273070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1333356</t>
+          <t>1331130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2796953</t>
+          <t>2796411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2873873</t>
+          <t>2875407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53591</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>84645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>75944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112608</t>
+          <t>112656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136046</t>
+          <t>137232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183690</t>
+          <t>184515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465983</t>
+          <t>466763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497817</t>
+          <t>500201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>363804</t>
+          <t>363756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400512</t>
+          <t>400468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>844130</t>
+          <t>843305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>891774</t>
+          <t>890588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>528509</t>
+          <t>528764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>612482</t>
+          <t>612259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>951145</t>
+          <t>957519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1064005</t>
+          <t>1062880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1510894</t>
+          <t>1508901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1648760</t>
+          <t>1646994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2664061</t>
+          <t>2664284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2748034</t>
+          <t>2747779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2315192</t>
+          <t>2316317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2428052</t>
+          <t>2421678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5006981</t>
+          <t>5008747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5144847</t>
+          <t>5146840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>437669</t>
+          <t>438016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>507023</t>
+          <t>502662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>789706</t>
+          <t>789740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>862689</t>
+          <t>863641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1249020</t>
+          <t>1255918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1346205</t>
+          <t>1350807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467620</t>
+          <t>471981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>536974</t>
+          <t>536627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>475108</t>
+          <t>474156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548091</t>
+          <t>548057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>966235</t>
+          <t>961633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1063420</t>
+          <t>1056522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>293121</t>
+          <t>293416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367101</t>
+          <t>363315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>452065</t>
+          <t>453214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>531480</t>
+          <t>534351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>770824</t>
+          <t>769352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>871956</t>
+          <t>875236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1596856</t>
+          <t>1600642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670836</t>
+          <t>1670541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1226323</t>
+          <t>1223452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1305738</t>
+          <t>1304589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2849804</t>
+          <t>2846524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2950936</t>
+          <t>2952408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>80953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86416</t>
+          <t>88045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>126935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>142758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195005</t>
+          <t>194087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400816</t>
+          <t>400228</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432743</t>
+          <t>432628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334088</t>
+          <t>331696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372215</t>
+          <t>370586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>744808</t>
+          <t>745726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794103</t>
+          <t>797055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>809982</t>
+          <t>815131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>919467</t>
+          <t>919668</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1364796</t>
+          <t>1361805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1479250</t>
+          <t>1482487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2207496</t>
+          <t>2205569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2371036</t>
+          <t>2358641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2500315</t>
+          <t>2500114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2609800</t>
+          <t>2604651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2074980</t>
+          <t>2071743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2189434</t>
+          <t>2192425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4602976</t>
+          <t>4615371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4766516</t>
+          <t>4768443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>290230</t>
+          <t>293561</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344907</t>
+          <t>344893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>565894</t>
+          <t>564739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>628840</t>
+          <t>627330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>870547</t>
+          <t>873496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>956131</t>
+          <t>960436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409440</t>
+          <t>409454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464117</t>
+          <t>460786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365820</t>
+          <t>367330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428766</t>
+          <t>429921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>792876</t>
+          <t>788571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>878460</t>
+          <t>875511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>330725</t>
+          <t>332053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>401559</t>
+          <t>401943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>488206</t>
+          <t>489864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568844</t>
+          <t>568870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>841305</t>
+          <t>839673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>947224</t>
+          <t>944871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1674826</t>
+          <t>1674442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1745660</t>
+          <t>1744332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1419456</t>
+          <t>1419430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1500094</t>
+          <t>1498436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3117461</t>
+          <t>3119814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3223380</t>
+          <t>3225012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109355</t>
+          <t>110837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171582</t>
+          <t>169895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221947</t>
+          <t>221752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437531</t>
+          <t>436049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473950</t>
+          <t>473328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>424417</t>
+          <t>423081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>460966</t>
+          <t>462807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874080</t>
+          <t>874275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>924445</t>
+          <t>926132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>722350</t>
+          <t>728973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>827273</t>
+          <t>822183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1175342</t>
+          <t>1177354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1294202</t>
+          <t>1293558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1934881</t>
+          <t>1933488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2092409</t>
+          <t>2085670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2550345</t>
+          <t>2555435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2655268</t>
+          <t>2648645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2237898</t>
+          <t>2238542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2356758</t>
+          <t>2354746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4817309</t>
+          <t>4824048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4974837</t>
+          <t>4976230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240475</t>
+          <t>239805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282928</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>493143</t>
+          <t>492598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>533093</t>
+          <t>532950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>743994</t>
+          <t>741298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>803526</t>
+          <t>803098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>233313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274463</t>
+          <t>275133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222415</t>
+          <t>222558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262365</t>
+          <t>262910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>466920</t>
+          <t>467348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526452</t>
+          <t>529148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>386634</t>
+          <t>367702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>619896</t>
+          <t>617500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724188</t>
+          <t>723733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1261774</t>
+          <t>1206531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1211672</t>
+          <t>1184618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1899616</t>
+          <t>1876661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1670431</t>
+          <t>1672827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1903693</t>
+          <t>1922625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>976049</t>
+          <t>1031292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1513635</t>
+          <t>1514090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2628534</t>
+          <t>2651489</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3316478</t>
+          <t>3343532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136888</t>
+          <t>137389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181082</t>
+          <t>182330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169430</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210766</t>
+          <t>209570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320307</t>
+          <t>319220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377320</t>
+          <t>380559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465541</t>
+          <t>464293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509735</t>
+          <t>509234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449697</t>
+          <t>450893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491033</t>
+          <t>491378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>929766</t>
+          <t>926527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>986779</t>
+          <t>987866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>740790</t>
+          <t>733530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1057219</t>
+          <t>1048900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1430840</t>
+          <t>1427766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1969666</t>
+          <t>1943108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2283661</t>
+          <t>2286912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2993426</t>
+          <t>2931131</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2394670</t>
+          <t>2402989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2711099</t>
+          <t>2718359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1684128</t>
+          <t>1710686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2222954</t>
+          <t>2226028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4112257</t>
+          <t>4174552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4822022</t>
+          <t>4818771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>316134</t>
+          <t>317125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>373968</t>
+          <t>375827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>588816</t>
+          <t>595529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>662520</t>
+          <t>669451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>927905</t>
+          <t>926541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1018300</t>
+          <t>1017974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657755</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>715589</t>
+          <t>714598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652593</t>
+          <t>645662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>726297</t>
+          <t>719584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1328535</t>
+          <t>1328861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1418930</t>
+          <t>1420294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134719</t>
+          <t>136327</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183643</t>
+          <t>183039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256543</t>
+          <t>254597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314603</t>
+          <t>316206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>405679</t>
+          <t>411709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484675</t>
+          <t>485740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1509770</t>
+          <t>1510374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1558694</t>
+          <t>1557086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1273070</t>
+          <t>1271467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1331130</t>
+          <t>1333076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2796411</t>
+          <t>2795346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2875407</t>
+          <t>2869377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51207</t>
+          <t>53350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84645</t>
+          <t>83264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75944</t>
+          <t>77730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112656</t>
+          <t>113362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137232</t>
+          <t>135619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184515</t>
+          <t>185064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466763</t>
+          <t>468144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500201</t>
+          <t>498058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>363756</t>
+          <t>363050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400468</t>
+          <t>398682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>843305</t>
+          <t>842756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>890588</t>
+          <t>892201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>528764</t>
+          <t>531817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>612259</t>
+          <t>613638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957519</t>
+          <t>956577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1062880</t>
+          <t>1067183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1508901</t>
+          <t>1507175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1646994</t>
+          <t>1650446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2664284</t>
+          <t>2662905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2747779</t>
+          <t>2744726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2316317</t>
+          <t>2312014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2421678</t>
+          <t>2422620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5008747</t>
+          <t>5005295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5146840</t>
+          <t>5148566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>438016</t>
+          <t>439814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>502662</t>
+          <t>503196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>789740</t>
+          <t>790416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>863641</t>
+          <t>860854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1255918</t>
+          <t>1250190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1350807</t>
+          <t>1350501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471981</t>
+          <t>471447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>536627</t>
+          <t>534829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>474156</t>
+          <t>476943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548057</t>
+          <t>547381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>961633</t>
+          <t>961939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1056522</t>
+          <t>1062250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>293416</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363315</t>
+          <t>364483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>453214</t>
+          <t>455046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>534351</t>
+          <t>535006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769352</t>
+          <t>770215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>875236</t>
+          <t>877976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1600642</t>
+          <t>1599474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1670541</t>
+          <t>1667033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1223452</t>
+          <t>1222797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1304589</t>
+          <t>1302757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2846524</t>
+          <t>2843784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2952408</t>
+          <t>2951545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>48296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80953</t>
+          <t>80875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88045</t>
+          <t>86328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126935</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142758</t>
+          <t>141361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194087</t>
+          <t>193759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400228</t>
+          <t>400306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432628</t>
+          <t>432885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331696</t>
+          <t>333823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>370586</t>
+          <t>372303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>745726</t>
+          <t>746054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>797055</t>
+          <t>798452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>815131</t>
+          <t>811545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>919668</t>
+          <t>917504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1361805</t>
+          <t>1360238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1482487</t>
+          <t>1480349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2205569</t>
+          <t>2200113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2358641</t>
+          <t>2368078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2500114</t>
+          <t>2502278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2604651</t>
+          <t>2608237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2071743</t>
+          <t>2073881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2192425</t>
+          <t>2193992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4615371</t>
+          <t>4605934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4768443</t>
+          <t>4773899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293561</t>
+          <t>290673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344893</t>
+          <t>342654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>564739</t>
+          <t>563474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>627330</t>
+          <t>627521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>873496</t>
+          <t>870907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>960436</t>
+          <t>956729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409454</t>
+          <t>411693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460786</t>
+          <t>463674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>367330</t>
+          <t>367139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429921</t>
+          <t>431186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>788571</t>
+          <t>792278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>875511</t>
+          <t>878100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>332053</t>
+          <t>334325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>401943</t>
+          <t>403773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>489864</t>
+          <t>489380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568870</t>
+          <t>574262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839673</t>
+          <t>838562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>944871</t>
+          <t>946806</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1674442</t>
+          <t>1672612</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1744332</t>
+          <t>1742060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1419430</t>
+          <t>1414038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1498436</t>
+          <t>1498920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3119814</t>
+          <t>3117879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3225012</t>
+          <t>3226123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110837</t>
+          <t>111077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86333</t>
+          <t>87618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126059</t>
+          <t>126800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169895</t>
+          <t>169407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221752</t>
+          <t>225599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436049</t>
+          <t>435809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473328</t>
+          <t>472621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423081</t>
+          <t>422340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462807</t>
+          <t>461522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>874275</t>
+          <t>870428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926132</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>728973</t>
+          <t>731066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>822183</t>
+          <t>824359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1177354</t>
+          <t>1169525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1293558</t>
+          <t>1290386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1933488</t>
+          <t>1931146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2085670</t>
+          <t>2078317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2555435</t>
+          <t>2553259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2648645</t>
+          <t>2646552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2238542</t>
+          <t>2241714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2354746</t>
+          <t>2362575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4824048</t>
+          <t>4831401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4976230</t>
+          <t>4978572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>260578</t>
+          <t>275528</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>239805</t>
+          <t>251927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281625</t>
+          <t>299650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>513374</t>
+          <t>550270</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>492598</t>
+          <t>525187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>532950</t>
+          <t>570757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>773953</t>
+          <t>825798</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>741298</t>
+          <t>790129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>803098</t>
+          <t>856706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>254360</t>
+          <t>303001</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233313</t>
+          <t>278879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275133</t>
+          <t>326602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>242134</t>
+          <t>271768</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222558</t>
+          <t>251281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262910</t>
+          <t>296851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>496493</t>
+          <t>574769</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>467348</t>
+          <t>543861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529148</t>
+          <t>610438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>538991</t>
+          <t>590372</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367702</t>
+          <t>549548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>617500</t>
+          <t>639156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>880613</t>
+          <t>742310</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>723733</t>
+          <t>698030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1206531</t>
+          <t>778974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1419604</t>
+          <t>1332683</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1184618</t>
+          <t>1278565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1876661</t>
+          <t>1397920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1751336</t>
+          <t>1640194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1672827</t>
+          <t>1591410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1922625</t>
+          <t>1681018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1357210</t>
+          <t>1429082</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1031292</t>
+          <t>1392418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1514090</t>
+          <t>1473362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3108546</t>
+          <t>3069276</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2651489</t>
+          <t>3004039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3343532</t>
+          <t>3123394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>159208</t>
+          <t>177316</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137389</t>
+          <t>155621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182330</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188931</t>
+          <t>214778</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169085</t>
+          <t>195983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209570</t>
+          <t>238160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>348138</t>
+          <t>392094</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319220</t>
+          <t>358663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>380559</t>
+          <t>422852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>487415</t>
+          <t>534271</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464293</t>
+          <t>510991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509234</t>
+          <t>555966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>471532</t>
+          <t>520099</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450893</t>
+          <t>496717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491378</t>
+          <t>538894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>958948</t>
+          <t>1054370</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926527</t>
+          <t>1023612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>987866</t>
+          <t>1087801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>958778</t>
+          <t>1043216</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>733530</t>
+          <t>982835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1048900</t>
+          <t>1095325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1582918</t>
+          <t>1507359</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1427766</t>
+          <t>1457437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1943108</t>
+          <t>1560700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2541696</t>
+          <t>2550575</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2286912</t>
+          <t>2464344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2931131</t>
+          <t>2626601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2493111</t>
+          <t>2477467</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2402989</t>
+          <t>2425358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2718359</t>
+          <t>2537848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2070876</t>
+          <t>2220948</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1710686</t>
+          <t>2167607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2226028</t>
+          <t>2270870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4563987</t>
+          <t>4698415</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4174552</t>
+          <t>4622389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4818771</t>
+          <t>4784646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
